--- a/templates/Excapism_Passenger_Upload_Template.xlsx
+++ b/templates/Excapism_Passenger_Upload_Template.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +91,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -466,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -479,8 +480,10 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,11 +503,13 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One row per passenger, starting at row 5. Required: Full Name, Trip Type, Country. Route, Ticket Purchaser and the rest are optional. Do not rename the headers.</t>
+          <t>One row per passenger, starting at row 5. Required: Full Name, Trip Type, Country. Route, Package Amount, Deposit Paid and the rest are optional. Do not rename the headers.</t>
         </is>
       </c>
     </row>
@@ -556,15 +561,25 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
+          <t>Package Amount (RM)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Deposit Paid (RM)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
           <t>Ticket Purchaser</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Medical Condition/ history if applicable</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -616,36 +631,45 @@
           <t>Surabaya - Bromo - Malang</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Excapism</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Sample row – delete or overwrite</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>↑ Sample row shown for format only – overwrite or delete it before uploading.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="G5:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open Trip,Private Trip"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Excapism,Self"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J5:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Number only" error="Enter a number such as 2400" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -658,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -666,236 +690,268 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>How to use this template</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
+      <c r="B1" s="8" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="7" t="n"/>
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>1. Fill in one row per passenger on the 'Passenger Upload' sheet, starting at row 5 (the sample row – delete or overwrite it).</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="B3" s="8" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2. Do not rename or remove the header row (row 4) – the app matches columns by their name. Column order does not matter.</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>3. 'Trip Type' + 'Country' + 'Route' decide which trip a passenger lands in: rows with the same three values go into the same trip, and a new trip is created if none exists yet. If Route is left blank, the passenger joins any existing trip for that Trip Type + Country.</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>4. Only 'Full Name (As per IC)', 'Trip Type' and 'Country' are required. Everything else can be left blank.</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>5. Routes you type here are remembered automatically in Admin &gt; Operations lists for that country.</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>6. Save as .xlsx or .csv, then use 'Bulk upload' in the app and drop the file in.</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>6. Package Amount and Deposit Paid: type the same amount down the column (copy-down) so you do not have to enter them one by one in the app. The payment status is set automatically: no deposit = Pending, some deposit = Deposit, deposit equal to the package = Paid.</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>7. Payment status, amount and deposit are not set from this sheet – every imported passenger starts as 'Pending' and can be updated in the app afterwards.</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>7. The upload preview shows package / deposit totals per trip and flags rows with a figure that is not a number or a deposit larger than the package. Flagged figures are imported as RM 0 – fix the sheet and re-upload if needed.</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>8. Save as .xlsx or .csv, then use 'Bulk upload' in the app and drop the file in.</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Column reference</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Full Name (As per IC)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Required. Passenger's full legal name.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Date of Birth (D.O.B)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Optional. Format YYYY-MM-DD.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>IC/Passport</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Optional. IC number (Malaysians) or passport number.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Contact Number</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Optional. Mobile number with country code.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Passport Number</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Optional.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Passport Expiry</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Optional. Format YYYY-MM-DD.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Trip Type</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Required. 'Open Trip' or 'Private Trip'.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Required. e.g. Indonesia, Japan, Vietnam. (An older 'Bali, Indonesia' style still works: the country is detected and 'Bali' becomes the route.)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Optional. e.g. Surabaya - Bromo - Malang. Separates trips to the same country with different itineraries.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Package Amount (RM)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Optional. Total package price for this passenger, numbers only (e.g. 2400). 'RM 2,400' also works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Deposit Paid (RM)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Optional. Deposit already received, numbers only. Cannot be more than the package amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Ticket Purchaser</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Optional. 'Excapism' (we buy the ticket) or 'Self' (passenger buys it). Leave blank if not decided.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Medical Condition/ history if applicable</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Optional. Leave blank if none.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Optional. Any additional remarks.</t>
         </is>
